--- a/data/export/2026-10-09-浦东35路.xlsx
+++ b/data/export/2026-10-09-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>1/20</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -945,7 +945,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1056,7 +1056,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1397,22 +1397,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1445,12 +1445,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1500,7 +1500,1339 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-浦东35路.xlsx
+++ b/data/export/2026-10-09-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -753,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -780,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/20</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -862,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -895,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -919,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -939,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1045,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1056,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1100,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq37，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1117,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1125,10 +1141,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1167,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1278,7 +1310,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1389,7 +1421,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1500,7 +1532,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1611,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1722,7 +1754,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1833,7 +1865,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1944,7 +1976,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2037,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2055,7 +2087,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2148,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2166,7 +2198,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2277,7 +2309,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2370,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2388,7 +2420,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2481,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2499,7 +2531,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2592,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2610,7 +2642,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2703,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2721,7 +2753,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2814,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2832,7 +2864,1236 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-浦东35路.xlsx
+++ b/data/export/2026-10-09-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -761,19 +761,19 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq37，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq64，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1227,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1260,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1284,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1449,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1482,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1506,33 +1518,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1632,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1704,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1743,7 +1759,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1815,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1893,12 +1909,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1926,7 +1942,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1934,10 +1950,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2037,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,7 +2180,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2226,12 +2258,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq40，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2259,7 +2291,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2267,10 +2299,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2370,7 +2418,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2529,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,7 +2640,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2703,7 +2751,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,7 +2862,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2925,7 +2973,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3036,7 +3084,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3147,7 +3195,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3258,7 +3306,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3369,7 +3417,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3480,7 +3528,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3591,7 +3639,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3702,7 +3750,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3770,7 +3818,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3813,7 +3861,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3827,7 +3875,7 @@
       <c r="T30" s="2" t="inlineStr"/>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3862,12 +3910,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3976,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3990,22 +4038,22 @@
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4043,7 +4091,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4057,7 +4105,7 @@
       <c r="T32" s="2" t="inlineStr"/>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4087,11 +4135,800 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr"/>
-      <c r="AC32" s="2" t="inlineStr">
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
         <is>
           <t>—/28</t>
         </is>

--- a/data/export/2026-10-09-浦东35路.xlsx
+++ b/data/export/2026-10-09-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1687,32 +1687,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1720,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1744,17 +1748,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1764,13 +1768,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1798,32 +1806,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1831,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1855,33 +1867,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1930,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq62，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1942,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2036,32 +2052,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2069,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2093,33 +2113,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2219,7 +2243,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2263,7 +2287,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq40，推进3站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq62，推进25站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2291,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2418,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2457,7 +2481,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2496,32 +2520,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2529,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2553,33 +2581,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2679,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2751,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2790,7 +2822,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2862,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2973,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,7 +3116,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,7 +3227,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,7 +3338,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,7 +3449,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3528,7 +3560,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3639,7 +3671,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3750,7 +3782,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3861,7 +3893,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3915,7 +3947,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3976,7 +4008,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4091,7 +4123,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4206,7 +4238,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4317,7 +4349,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4428,7 +4460,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4482,7 +4514,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4575,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4654,7 +4686,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4769,7 +4801,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4880,7 +4912,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4924,11 +4956,804 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr"/>
-      <c r="AC39" s="2" t="inlineStr">
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
         <is>
           <t>—/28</t>
         </is>

--- a/data/export/2026-10-09-浦东35路.xlsx
+++ b/data/export/2026-10-09-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC46"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3194,32 +3194,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3227,7 +3231,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3251,17 +3255,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3271,13 +3275,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3346,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3449,7 +3457,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3560,7 +3568,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,7 +3679,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,7 +3790,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,7 +3901,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3947,7 +3955,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4016,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,7 +4131,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4177,7 +4185,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4246,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4349,7 +4357,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4460,7 +4468,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4514,7 +4522,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4583,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4686,7 +4694,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4740,7 +4748,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4809,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4912,7 +4920,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4966,7 +4974,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5035,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5081,7 +5089,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5204,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5265,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5368,7 +5376,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5479,7 +5487,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5533,7 +5541,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5602,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5705,7 +5713,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5759,6 +5767,228 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-09-浦东35路.xlsx
+++ b/data/export/2026-10-09-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,18 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,13 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1724,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2442,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2783,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2894,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3005,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,32 +3091,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3116,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3140,17 +3152,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3160,13 +3172,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3204,24 +3220,24 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3231,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3270,22 +3286,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3313,32 +3329,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3346,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3370,33 +3390,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3424,32 +3448,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3457,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3481,17 +3509,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3501,13 +3529,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3535,32 +3567,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3568,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3592,17 +3628,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3612,13 +3648,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3646,32 +3686,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -3679,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3703,33 +3747,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3757,32 +3805,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3790,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3814,33 +3866,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3868,32 +3924,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3901,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3925,17 +3985,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3945,17 +4005,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4070,7 +4130,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4098,32 +4158,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4131,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4155,37 +4219,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4213,32 +4277,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4246,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4270,33 +4338,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB33" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4324,12 +4396,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4357,7 +4429,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4365,10 +4437,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4468,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4522,7 +4610,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4550,32 +4638,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4583,7 +4675,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4607,17 +4699,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4627,13 +4719,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB36" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4790,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4748,7 +4844,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4905,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4848,7 +4944,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4920,7 +5016,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4974,7 +5070,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5035,7 +5131,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5089,7 +5185,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5246,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5204,7 +5300,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5361,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5376,7 +5472,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5487,7 +5583,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5541,7 +5637,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5698,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5713,7 +5809,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5824,7 +5920,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5935,7 +6031,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5989,6 +6085,807 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-09-浦东35路.xlsx
+++ b/data/export/2026-10-09-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,13 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,7 +2025,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2032,7 +2036,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2145,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,18 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2378,7 +2386,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2389,7 +2397,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2494,13 +2502,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,17 +2621,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2730,7 +2742,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2842,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2841,7 +2853,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2952,7 +2964,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3063,7 +3075,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3301,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3420,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3777,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3896,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4142,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4249,7 +4261,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4368,7 +4380,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4413,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4429,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4495,7 +4507,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4610,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4648,12 +4660,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -4675,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4724,12 +4736,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4829,7 +4841,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4844,7 +4856,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4872,32 +4884,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4905,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4929,17 +4945,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4949,13 +4965,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4983,32 +5003,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5016,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5040,17 +5064,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5060,17 +5084,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5098,32 +5122,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5131,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5155,17 +5183,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5175,17 +5203,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5213,32 +5241,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5246,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5270,17 +5302,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5290,17 +5322,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5328,32 +5360,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5361,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5385,33 +5421,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5439,32 +5479,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5472,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5496,17 +5540,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5516,13 +5560,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5550,32 +5598,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5583,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5607,17 +5659,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5627,17 +5679,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5748,7 +5800,7 @@
       <c r="AB45" s="2" t="inlineStr"/>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5848,7 +5900,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5859,7 +5911,7 @@
       <c r="AB46" s="2" t="inlineStr"/>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5970,7 +6022,7 @@
       <c r="AB47" s="2" t="inlineStr"/>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6083,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6081,7 +6133,7 @@
       <c r="AB48" s="2" t="inlineStr"/>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6142,7 +6194,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6196,7 +6248,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6309,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6311,7 +6363,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6424,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6426,7 +6478,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6539,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6541,7 +6593,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6654,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6656,7 +6708,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6769,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6771,7 +6823,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6832,7 +6884,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6876,13 +6928,691 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB55" s="2" t="inlineStr"/>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>—/28</t>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-浦东35路.xlsx
+++ b/data/export/2026-10-09-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,13 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2847,13 +2851,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,13 +2966,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,18 +3076,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,17 +3314,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3378,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3422,17 +3438,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,14 +3552,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>149.0</t>
@@ -3551,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,22 +3790,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3898,17 +3914,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4261,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4380,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4856,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4975,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5348,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5451,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,7 +5571,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5570,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5608,12 +5624,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -5635,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5684,12 +5700,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5717,32 +5733,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5750,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5774,17 +5794,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5794,13 +5814,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5828,32 +5852,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5861,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5885,17 +5913,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5905,13 +5933,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5939,32 +5971,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5972,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5996,17 +6032,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6016,13 +6052,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6050,32 +6090,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6083,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6107,33 +6151,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB48" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6161,32 +6209,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6194,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6218,32 +6270,32 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6276,32 +6328,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6309,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6333,17 +6389,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6353,17 +6409,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6391,32 +6447,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -6424,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6448,37 +6508,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6506,32 +6566,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6539,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6563,17 +6627,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6583,17 +6647,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6708,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6823,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6938,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6999,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7053,7 +7117,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7225,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7336,7 +7400,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7390,7 +7454,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7562,7 +7626,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7606,13 +7670,592 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB61" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-浦东35路.xlsx
+++ b/data/export/2026-10-09-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>146.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,14 +1894,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>146.5</t>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2025,18 +2025,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2331,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2458,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2631,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2976,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3210,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3567,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3800,7 +3804,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3870,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3989,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,14 +4032,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>146.0</t>
@@ -4043,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4267,17 +4271,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,22 +4385,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,7 +4746,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4818,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4862,17 +4866,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,22 +4980,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,14 +5218,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>146.5</t>
@@ -5229,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5532,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5705,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6062,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6246,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6300,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6457,24 +6461,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6484,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6533,7 +6537,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6603,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6685,32 +6689,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6718,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6742,37 +6750,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6800,32 +6808,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6833,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6857,17 +6869,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6877,17 +6889,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6915,32 +6927,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -6948,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6972,37 +6988,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7030,32 +7046,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7063,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7087,17 +7107,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7107,17 +7127,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7165,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq51，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7178,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7186,10 +7206,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr"/>
-      <c r="S57" s="2" t="inlineStr"/>
-      <c r="T57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq38（站名待映射） ETA 4分钟参与校验</t>
+        </is>
+      </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -7256,32 +7292,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7289,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7313,33 +7353,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7515,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7626,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7741,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7856,7 +7900,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7910,7 +7954,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7971,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8086,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8135,7 +8179,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8201,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8255,7 +8299,697 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-浦东35路.xlsx
+++ b/data/export/2026-10-09-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2144,14 +2144,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>151.5</t>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2264,17 +2264,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2395,13 +2395,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2506,17 +2510,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,17 +2859,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3095,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,14 +3203,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>155.0</t>
@@ -3214,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3323,17 +3327,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3456,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3571,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3809,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4047,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4400,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4516,7 +4520,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4527,7 +4531,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4761,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4876,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4990,12 +4994,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5233,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,14 +5341,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>151.5</t>
@@ -5352,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5461,17 +5465,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5580,17 +5584,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5937,17 +5941,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6185,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6294,17 +6298,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6542,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6780,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6937,24 +6941,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6964,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7013,12 +7017,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7068,12 +7072,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7083,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7137,7 +7141,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7174,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq51，推进13站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq56，推进18站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7198,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7264,7 +7268,7 @@
       <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7302,12 +7306,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -7329,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7378,12 +7382,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7411,32 +7415,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7444,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7468,17 +7476,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7488,17 +7496,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7526,32 +7534,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7559,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7583,17 +7595,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7603,13 +7615,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7637,32 +7653,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7670,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7694,17 +7714,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7714,17 +7734,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7752,32 +7772,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7785,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7809,17 +7833,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7829,17 +7853,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7867,32 +7891,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7900,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7924,17 +7952,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7944,17 +7972,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8069,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8184,7 +8212,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8299,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8414,7 +8442,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8529,7 +8557,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8639,12 +8667,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8705,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8759,7 +8787,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8869,12 +8897,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8882,22 +8910,22 @@
       <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8930,12 +8958,12 @@
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8979,17 +9007,469 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
+      <c r="AB73" s="2" t="inlineStr">
         <is>
           <t>146.5</t>
         </is>
       </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>21/29</t>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>151.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-浦东35路.xlsx
+++ b/data/export/2026-10-09-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC76"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3560,22 +3560,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3803,17 +3803,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4394,17 +4394,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6179,17 +6179,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6536,17 +6536,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6774,17 +6774,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8010,32 +8010,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -8043,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8067,17 +8071,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8087,17 +8091,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8125,32 +8129,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -8158,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8182,17 +8190,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8202,17 +8210,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8240,32 +8248,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8273,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,37 +8309,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8355,32 +8367,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8388,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8412,17 +8428,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8432,17 +8448,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8470,32 +8486,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8503,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8527,17 +8547,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8547,12 +8567,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8618,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8672,7 +8692,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8787,7 +8807,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8963,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9074,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9128,7 +9148,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9209,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9300,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9415,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9473,6 +9493,1041 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>9/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>135.3</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>144.5</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-09-浦东35路.xlsx
+++ b/data/export/2026-10-09-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC85"/>
+  <dimension ref="A1:AC88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4755,17 +4755,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8720,32 +8720,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8753,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8777,17 +8781,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8797,17 +8801,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8922,7 +8926,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9094,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9320,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9435,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9550,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9665,7 +9669,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9780,7 +9784,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9895,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9949,7 +9953,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10014,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10064,7 +10068,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10125,7 +10129,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10179,7 +10183,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10240,7 +10244,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10294,7 +10298,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10359,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10409,7 +10413,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10474,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10519,12 +10523,357 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-浦东35路.xlsx
+++ b/data/export/2026-10-09-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC88"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>143.7</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,14 +4036,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>143.7</t>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5227,17 +5227,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8562,14 +8562,14 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
           <t>143.7</t>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8605,32 +8605,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8638,7 +8642,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8662,17 +8666,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8682,7 +8686,7 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8730,12 +8734,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -8757,7 +8761,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8796,7 +8800,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8806,7 +8810,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8872,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8954,12 +8958,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程32%处后消失；随后反向物理轨迹由seq28推进至seq44，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -8987,7 +8991,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8995,10 +8999,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q72" s="2" t="inlineStr"/>
-      <c r="R72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路云山路</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="S72" s="2" t="inlineStr"/>
-      <c r="T72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq21映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -9065,32 +9081,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9098,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9122,17 +9142,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9142,17 +9162,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9324,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9439,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9554,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9669,7 +9689,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9784,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9899,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10014,7 +10034,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10129,7 +10149,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10244,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10359,7 +10379,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10474,7 +10494,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10528,7 +10548,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10589,7 +10609,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10704,7 +10724,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10819,7 +10839,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10877,6 +10897,351 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>143.7</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-09-浦东35路.xlsx
+++ b/data/export/2026-10-09-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2025,17 +2025,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2395,17 +2395,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2744,17 +2744,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3203,22 +3203,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,22 +3679,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5222,22 +5222,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5346,17 +5346,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5822,17 +5822,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7372,17 +7372,17 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7615,17 +7615,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8734,24 +8734,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8843,32 +8843,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8876,7 +8880,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8900,32 +8904,32 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8963,7 +8967,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程32%处后消失；随后反向物理轨迹由seq28推进至seq44，推进16站，达到≥2站确认条件</t>
+          <t>原方向在全程32%处后消失；随后反向物理轨迹由seq28推进至seq59，推进31站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -8991,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9091,12 +9095,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
@@ -9118,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9157,22 +9161,22 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9311,32 +9315,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9344,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9368,37 +9376,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9426,32 +9434,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9459,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9483,17 +9495,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9503,17 +9515,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9541,32 +9553,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9574,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9598,37 +9614,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9656,32 +9672,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9689,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9713,17 +9733,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9733,17 +9753,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9771,32 +9791,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9804,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9828,17 +9852,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9848,17 +9872,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -9919,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10034,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10149,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10203,7 +10227,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10379,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10494,7 +10518,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10548,7 +10572,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10633,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10724,7 +10748,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10778,7 +10802,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -10839,7 +10863,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10893,7 +10917,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10978,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11008,7 +11032,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -11069,7 +11093,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11184,7 +11208,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11233,12 +11257,817 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-浦东35路.xlsx
+++ b/data/export/2026-10-09-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC98"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,17 +1775,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,22 +3441,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3565,17 +3565,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,22 +3917,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,22 +4151,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,17 +5103,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6412,22 +6412,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6650,22 +6650,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6893,17 +6893,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8329,17 +8329,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -9682,24 +9682,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9801,24 +9801,24 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -9910,32 +9910,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9943,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9967,37 +9971,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10025,32 +10029,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10058,7 +10066,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10082,37 +10090,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10140,32 +10148,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10173,7 +10185,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10197,37 +10209,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10255,32 +10267,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10288,7 +10304,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10312,32 +10328,32 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10370,32 +10386,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10403,7 +10423,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10427,17 +10447,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10447,17 +10467,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10485,32 +10505,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10518,7 +10542,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10542,17 +10566,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10562,17 +10586,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10633,7 +10657,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10687,7 +10711,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10748,7 +10772,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10787,7 +10811,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10863,7 +10887,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10978,7 +11002,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11032,7 +11056,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -11093,7 +11117,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11147,7 +11171,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11208,7 +11232,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11262,7 +11286,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -11323,7 +11347,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11377,7 +11401,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11462,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11492,7 +11516,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11553,7 +11577,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11607,7 +11631,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -11668,7 +11692,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11722,7 +11746,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -11783,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11898,7 +11922,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11952,7 +11976,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -11960,22 +11984,22 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -12008,12 +12032,12 @@
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12027,47 +12051,967 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>137.7</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W98" s="2" t="inlineStr">
+      <c r="W99" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X98" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y98" s="2" t="inlineStr">
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z98" s="2" t="inlineStr">
+      <c r="Z99" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA98" s="2" t="inlineStr">
+      <c r="AA99" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB98" s="2" t="inlineStr">
+      <c r="AB99" s="2" t="inlineStr">
         <is>
           <t>137.5</t>
         </is>
       </c>
-      <c r="AC98" s="2" t="inlineStr">
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>137.7</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
         <is>
           <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-浦东35路.xlsx
+++ b/data/export/2026-10-09-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC106"/>
+  <dimension ref="A1:AC108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2264,17 +2264,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2859,17 +2859,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3327,17 +3327,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4755,17 +4755,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4870,17 +4870,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5465,17 +5465,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5941,17 +5941,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6298,17 +6298,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7131,17 +7131,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7496,17 +7496,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7734,17 +7734,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7972,17 +7972,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8805,17 +8805,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10304,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10396,12 +10396,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10515,24 +10515,24 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10591,12 +10591,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10624,32 +10624,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10657,7 +10661,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10681,17 +10685,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10701,17 +10705,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10743,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10772,7 +10780,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10796,17 +10804,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10816,12 +10824,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10854,32 +10862,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10887,7 +10899,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10911,17 +10923,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10931,17 +10943,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10969,32 +10981,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11002,7 +11018,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11026,17 +11042,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11046,12 +11062,12 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11084,32 +11100,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11117,7 +11137,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11141,17 +11161,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11161,17 +11181,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -11199,32 +11219,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11232,7 +11256,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11256,17 +11280,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11276,17 +11300,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -11401,7 +11425,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -11462,7 +11486,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11501,7 +11525,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11516,7 +11540,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -11544,32 +11568,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11577,7 +11605,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11601,17 +11629,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11621,17 +11649,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11692,7 +11720,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11746,7 +11774,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11835,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11922,7 +11950,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11976,7 +12004,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12065,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12091,7 +12119,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -12152,7 +12180,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12206,7 +12234,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -12267,7 +12295,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12382,7 +12410,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12436,7 +12464,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -12497,7 +12525,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12551,7 +12579,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -12612,7 +12640,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12666,7 +12694,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12727,7 +12755,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12781,7 +12809,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -12789,22 +12817,22 @@
       <c r="A105" s="2" t="inlineStr"/>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -12837,12 +12865,12 @@
       <c r="M105" s="2" t="inlineStr"/>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12856,7 +12884,7 @@
       <c r="T105" s="2" t="inlineStr"/>
       <c r="U105" s="2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="V105" s="2" t="inlineStr">
@@ -12886,17 +12914,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -12904,7 +12932,7 @@
       <c r="A106" s="2" t="inlineStr"/>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -12914,7 +12942,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -12952,12 +12980,12 @@
       <c r="M106" s="2" t="inlineStr"/>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -12971,47 +12999,277 @@
       <c r="T106" s="2" t="inlineStr"/>
       <c r="U106" s="2" t="inlineStr">
         <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
           <t>20:30</t>
         </is>
       </c>
-      <c r="V106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W106" s="2" t="inlineStr">
+      <c r="W107" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X106" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y106" s="2" t="inlineStr">
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z106" s="2" t="inlineStr">
+      <c r="Z107" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA106" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB106" s="2" t="inlineStr">
-        <is>
-          <t>148.0</t>
-        </is>
-      </c>
-      <c r="AC106" s="2" t="inlineStr">
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-浦东35路.xlsx
+++ b/data/export/2026-10-09-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2744,17 +2744,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3208,17 +3208,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3684,17 +3684,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5227,17 +5227,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5346,17 +5346,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5822,17 +5822,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7853,12 +7853,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9166,17 +9166,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9396,17 +9396,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9515,17 +9515,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9634,17 +9634,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9872,17 +9872,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -10715,7 +10715,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -11425,7 +11425,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -11453,32 +11453,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11486,7 +11490,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11510,17 +11514,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11530,17 +11534,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -11605,7 +11609,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11687,32 +11691,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11720,7 +11728,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11744,17 +11752,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11764,12 +11772,12 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11802,32 +11810,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11835,7 +11847,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11859,17 +11871,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11879,17 +11891,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -11917,32 +11929,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11950,7 +11966,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11974,17 +11990,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11994,17 +12010,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -12032,12 +12048,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq29推进至seq58，推进29站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -12065,7 +12081,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12073,10 +12089,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q98" s="2" t="inlineStr"/>
-      <c r="R98" s="2" t="inlineStr"/>
-      <c r="S98" s="2" t="inlineStr"/>
-      <c r="T98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12147,32 +12179,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12180,7 +12216,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12204,17 +12240,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12224,17 +12260,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -12262,32 +12298,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -12295,7 +12335,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12319,17 +12359,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12339,17 +12379,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -12410,7 +12450,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12464,7 +12504,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12532,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq52，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -12525,7 +12565,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12533,10 +12573,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q102" s="2" t="inlineStr"/>
-      <c r="R102" s="2" t="inlineStr"/>
-      <c r="S102" s="2" t="inlineStr"/>
-      <c r="T102" s="2" t="inlineStr"/>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12640,7 +12696,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12694,7 +12750,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -12722,32 +12778,36 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -12755,7 +12815,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12779,17 +12839,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12799,17 +12859,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -12870,7 +12930,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12924,7 +12984,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -12985,7 +13045,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13039,7 +13099,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -13100,7 +13160,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13215,7 +13275,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13259,17 +13319,17 @@
       </c>
       <c r="AA108" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
